--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484085_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484085_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. BALTÀ CASTELLTORT</t>
+          <t>E. TEJERO CASASAYAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5282</v>
+        <v>0.8376</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0556</v>
+        <v>2.1973</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5274</v>
+        <v>-1.3597</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.6919</v>
+        <v>-1.0147</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.5247</v>
+        <v>-1.0936</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.1672</v>
+        <v>0.0789</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.892</v>
+        <v>1.9575</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.0527</v>
+        <v>0.2982</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1606</v>
+        <v>1.6594</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.7999</v>
+        <v>-2.9722</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.472</v>
+        <v>-1.3918</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3279</v>
+        <v>-1.5805</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9919</v>
+        <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5472</v>
+        <v>0.3713</v>
       </c>
       <c r="T2" t="n">
-        <v>3.146</v>
+        <v>0.0965</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4012</v>
+        <v>0.2748</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1206</v>
+        <v>0.2907</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.1352</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1206</v>
+        <v>-0.8445</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2454</v>
+        <v>0.3755</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3029</v>
+        <v>-0.2009</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5483</v>
+        <v>0.5763</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0454</v>
@@ -688,13 +688,13 @@
         <v>0.5952</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.106</v>
+        <v>0.0241</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1247</v>
+        <v>-0.0227</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. TEJERO CASASAYAS</t>
+          <t>R. MARIMON SOTERAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0049</v>
+        <v>-0.2593</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4208</v>
+        <v>-0.8389</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4158</v>
+        <v>0.5796</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0147</v>
+        <v>-0.5442</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0936</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0789</v>
+        <v>-0.5442</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9575</v>
+        <v>-0.6802</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2982</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6594</v>
+        <v>-0.6802</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9722</v>
+        <v>0.136</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3918</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5805</v>
+        <v>0.136</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1822</v>
+        <v>0.3968</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4614</v>
+        <v>0.0864</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.68</v>
+        <v>0.0397</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2187</v>
+        <v>0.0468</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2907</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1352</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CUMELLES CESPEDES</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.366</v>
+        <v>-0.4595</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1629</v>
+        <v>-0.5289</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2031</v>
+        <v>0.0693</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.7244</v>
+        <v>-1.4657</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3097</v>
+        <v>-0.0756</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4147</v>
+        <v>-1.3901</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.08</v>
+        <v>-0.2115</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1227</v>
+        <v>0.3884</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0427</v>
+        <v>-0.5999</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6444</v>
+        <v>-1.2542</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.187</v>
+        <v>-0.4639</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4574</v>
+        <v>-0.7902</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8082</v>
+        <v>-0.1842</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4285</v>
+        <v>-0.3174</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3797</v>
+        <v>0.1332</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7486</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. MARIMON SOTERAS</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3894</v>
+        <v>-0.5175</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9409</v>
+        <v>-0.9188</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5515</v>
+        <v>0.4013</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5442</v>
+        <v>-2.1479</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.6804</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5442</v>
+        <v>-2.8283</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6802</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.2755</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6802</v>
+        <v>-2.038</v>
       </c>
       <c r="M6" t="n">
-        <v>0.136</v>
+        <v>-1.3853</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.5951</v>
       </c>
       <c r="O6" t="n">
-        <v>0.136</v>
+        <v>-0.7902</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0436</v>
+        <v>0.5527</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0623</v>
+        <v>0.2325</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0187</v>
+        <v>0.3202</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4826</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>C. FONS TEIXIDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6881</v>
+        <v>-1.0671</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1455</v>
+        <v>1.7957</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4574</v>
+        <v>-2.8628</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1479</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6804</v>
+        <v>-0.1263</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.8283</v>
+        <v>-0.4237</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7625999999999999</v>
+        <v>1.2207</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2755</v>
+        <v>0.7311</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.038</v>
+        <v>0.4896</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3853</v>
+        <v>-1.7707</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5951</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7902</v>
+        <v>-0.9133</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3821</v>
+        <v>0.231</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0057</v>
+        <v>-0.0282</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3763</v>
+        <v>0.2592</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4826</v>
+        <v>-2.5336</v>
       </c>
       <c r="W7" t="n">
         <v>0.6032</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1206</v>
+        <v>-3.1368</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>A. CUMELLES CESPEDES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8217</v>
+        <v>-1.2985</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.835</v>
+        <v>-0.8148</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0132</v>
+        <v>-0.4837</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4657</v>
+        <v>-2.7244</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0756</v>
+        <v>-1.3097</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3901</v>
+        <v>-1.4147</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2115</v>
+        <v>-1.08</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3884</v>
+        <v>-1.1227</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5999</v>
+        <v>0.0427</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2542</v>
+        <v>-1.6444</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4639</v>
+        <v>-0.187</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7902</v>
+        <v>-1.4574</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5464</v>
+        <v>0.8757</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.7766</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0771</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.7486</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.7239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. FONS TEIXIDO</t>
+          <t>A. BALTÀ CASTELLTORT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0718</v>
+        <v>-1.5622</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7225</v>
+        <v>-1.6396</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-3.6919</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1263</v>
+        <v>-2.5247</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4237</v>
+        <v>-1.1672</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2207</v>
+        <v>-0.892</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7311</v>
+        <v>-1.0527</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4896</v>
+        <v>0.1606</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7707</v>
+        <v>-2.7999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.472</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9133</v>
+        <v>-1.3279</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7737000000000001</v>
+        <v>1.4568</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1732</v>
+        <v>1.1678</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3995</v>
+        <v>0.289</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.5336</v>
+        <v>-0.1206</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.1368</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3694</v>
+        <v>-3.0595</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7441</v>
+        <v>-2.2939</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6254</v>
+        <v>-0.7657</v>
       </c>
       <c r="G10" t="n">
         <v>-4.3238</v>
@@ -1234,13 +1234,13 @@
         <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>1.488</v>
+        <v>0.7978</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7937</v>
+        <v>0.2439</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6943</v>
+        <v>0.554</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7239</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9456</v>
+        <v>-5.2048</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6281</v>
+        <v>-3.0556</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3176</v>
+        <v>-2.1492</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8189</v>
@@ -1312,13 +1312,13 @@
         <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5622</v>
+        <v>0.1786</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3683</v>
+        <v>0.2042</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1939</v>
+        <v>-0.0256</v>
       </c>
       <c r="V11" t="n">
         <v>0.4113</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.7802</v>
+        <v>-5.8149</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.1143</v>
+        <v>-4.5418</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6659</v>
+        <v>-1.2731</v>
       </c>
       <c r="G12" t="n">
         <v>-4.9814</v>
@@ -1390,13 +1390,13 @@
         <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3672</v>
+        <v>0.5981</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0735</v>
+        <v>0.4989</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2937</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2413</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.6537</v>
+        <v>-18.0302</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.746599999999999</v>
+        <v>-9.1233</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.907300000000001</v>
+        <v>-8.907299999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-24.3082</v>
@@ -1447,19 +1447,19 @@
         <v>-2.5638</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2276000000000002</v>
+        <v>-0.2275999999999998</v>
       </c>
       <c r="M13" t="n">
         <v>-21.5169</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.630799999999999</v>
+        <v>-9.630800000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-11.886</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9758</v>
+        <v>2.975799999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.8949</v>
@@ -1468,10 +1468,10 @@
         <v>15.8708</v>
       </c>
       <c r="S13" t="n">
-        <v>4.364999999999999</v>
+        <v>4.9883</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2684</v>
+        <v>2.8918</v>
       </c>
       <c r="U13" t="n">
         <v>2.0966</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.231199999999999</v>
+        <v>9.4377</v>
       </c>
       <c r="E14" t="n">
-        <v>8.3095</v>
+        <v>8.2074</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9217</v>
+        <v>1.2303</v>
       </c>
       <c r="G14" t="n">
         <v>7.2918</v>
@@ -1546,13 +1546,13 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.132</v>
+        <v>-0.9254</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0056</v>
+        <v>-0.1076</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1264</v>
+        <v>-0.8177</v>
       </c>
       <c r="V14" t="n">
         <v>1.881</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.3602</v>
+        <v>5.6979</v>
       </c>
       <c r="E15" t="n">
-        <v>4.438</v>
+        <v>3.7238</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9222</v>
+        <v>1.974</v>
       </c>
       <c r="G15" t="n">
         <v>3.9784</v>
@@ -1624,13 +1624,13 @@
         <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1592</v>
+        <v>-0.5031</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3629</v>
+        <v>-0.3513</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2036</v>
+        <v>-0.1518</v>
       </c>
       <c r="V15" t="n">
         <v>3.0162</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3011</v>
+        <v>3.1966</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8938</v>
+        <v>1.0979</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4073</v>
+        <v>2.0987</v>
       </c>
       <c r="G16" t="n">
         <v>3.2892</v>
@@ -1702,13 +1702,13 @@
         <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9881</v>
+        <v>-1.0926</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8105</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1776</v>
+        <v>-0.4862</v>
       </c>
       <c r="V16" t="n">
         <v>0.6032</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9743</v>
+        <v>3.1145</v>
       </c>
       <c r="E17" t="n">
         <v>0.9746</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9997</v>
+        <v>2.14</v>
       </c>
       <c r="G17" t="n">
         <v>4.5926</v>
@@ -1780,13 +1780,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3009</v>
+        <v>-1.1606</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3117</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9892</v>
+        <v>-0.8489</v>
       </c>
       <c r="V17" t="n">
         <v>0.6745</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>A. TARRIDA TORRES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8105</v>
+        <v>0.7397</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5293</v>
+        <v>1.0102</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3398</v>
+        <v>-0.2705</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6896</v>
+        <v>1.531</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9276</v>
+        <v>-0.2271</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7619</v>
+        <v>1.7581</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6099</v>
+        <v>2.0361</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2886</v>
+        <v>0.0255</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3213</v>
+        <v>2.0106</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0797</v>
+        <v>-0.5051</v>
       </c>
       <c r="N18" t="n">
-        <v>0.639</v>
+        <v>-0.2525</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4406</v>
+        <v>-0.2526</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3806</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>0.395</v>
+        <v>0.4152</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0431</v>
+        <v>-0.0339</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.648</v>
+        <v>0.4491</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.317</v>
+        <v>0.4625</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6002</v>
+        <v>-0.0901</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9172</v>
+        <v>0.5525</v>
       </c>
       <c r="G19" t="n">
         <v>1.2234</v>
@@ -1936,13 +1936,13 @@
         <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.231</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7481</v>
+        <v>-0.238</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8337</v>
+        <v>0.469</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ PEREZ</t>
+          <t>R. RIBAS BLANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1547</v>
+        <v>0.1828</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1547</v>
+        <v>0.1828</v>
       </c>
       <c r="G20" t="n">
         <v>0.136</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. RIBAS BLANCO</t>
+          <t>P. RODRIGUEZ PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1547</v>
+        <v>0.1828</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1547</v>
+        <v>0.1828</v>
       </c>
       <c r="G21" t="n">
         <v>0.136</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. TARRIDA TORRES</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0264</v>
+        <v>0.0002</v>
       </c>
       <c r="E22" t="n">
-        <v>0.296</v>
+        <v>-1.4475</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3224</v>
+        <v>1.4478</v>
       </c>
       <c r="G22" t="n">
-        <v>1.531</v>
+        <v>1.6896</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2271</v>
+        <v>0.9276</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7581</v>
+        <v>0.7619</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0361</v>
+        <v>0.6099</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0255</v>
+        <v>0.2886</v>
       </c>
       <c r="L22" t="n">
-        <v>2.0106</v>
+        <v>0.3213</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5051</v>
+        <v>1.0797</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2525</v>
+        <v>0.639</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2526</v>
+        <v>0.4406</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9919</v>
+        <v>-2.1822</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>2.3806</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3509</v>
+        <v>-0.4153</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7481</v>
+        <v>0.1248</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3973</v>
+        <v>-0.5401</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.737</v>
+        <v>-0.7387</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.9537</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0893</v>
+        <v>0.2151</v>
       </c>
       <c r="G23" t="n">
         <v>0.1168</v>
@@ -2248,13 +2248,13 @@
         <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0521</v>
+        <v>-0.0538</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2438</v>
+        <v>-0.0623</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2959</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6032</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.889</v>
+        <v>-1.0744</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6244</v>
+        <v>-2.1143</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7355</v>
+        <v>1.0398</v>
       </c>
       <c r="G24" t="n">
         <v>1.0819</v>
@@ -2326,13 +2326,13 @@
         <v>1.9838</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0384</v>
+        <v>-0.2239</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7481</v>
+        <v>-0.238</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2903</v>
+        <v>0.0141</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9405</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9977</v>
+        <v>-1.8676</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6031</v>
+        <v>-1.5011</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3946</v>
+        <v>-0.3665</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7585</v>
@@ -2404,13 +2404,13 @@
         <v>0.1984</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1797</v>
+        <v>-0.0496</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3741</v>
+        <v>-0.272</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1944</v>
+        <v>0.2224</v>
       </c>
       <c r="V25" t="n">
         <v>-0.266</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>18.6536</v>
+        <v>19.334</v>
       </c>
       <c r="E26" t="n">
-        <v>8.907199999999998</v>
+        <v>8.9072</v>
       </c>
       <c r="F26" t="n">
-        <v>9.746499999999999</v>
+        <v>10.4268</v>
       </c>
       <c r="G26" t="n">
         <v>24.3082</v>
@@ -2458,7 +2458,7 @@
         <v>21.5169</v>
       </c>
       <c r="K26" t="n">
-        <v>9.6309</v>
+        <v>9.630900000000002</v>
       </c>
       <c r="L26" t="n">
         <v>11.886</v>
@@ -2482,16 +2482,16 @@
         <v>12.8949</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.364999999999999</v>
+        <v>-3.6845</v>
       </c>
       <c r="T26" t="n">
         <v>-2.0964</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.2682</v>
+        <v>-1.588</v>
       </c>
       <c r="V26" t="n">
-        <v>1.686299999999998</v>
+        <v>1.686299999999999</v>
       </c>
       <c r="W26" t="n">
         <v>5.3578</v>
